--- a/xlsx/packagedata20260413 special cargo-FR-GP.xlsx
+++ b/xlsx/packagedata20260413 special cargo-FR-GP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Collection\ReactThreejsFiber\Containerloadingsys\public\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C63B99C4-47BC-4823-A2DC-F5E1348BCEF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67CD5551-060F-4A69-B2B9-B89A5FECAF8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -87,19 +87,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>pkg02-54</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pkg04-52</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pkg03-53</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pkg01-55</t>
+    <t>pkg01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pkg02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pkg03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pkg04</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -491,7 +491,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B2">
         <v>350</v>
@@ -529,7 +529,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3">
         <v>330</v>
@@ -605,7 +605,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B5">
         <v>240</v>
